--- a/Exam/gymtrackerpro/app/admin/workout-sessions/new/_components/__tests__/ft/create-workout-session-form/create-workout-session-form-ft-form.xlsx
+++ b/Exam/gymtrackerpro/app/admin/workout-sessions/new/_components/__tests__/ft/create-workout-session-form/create-workout-session-form-ft-form.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="104">
   <si>
     <t>Component: CreateWorkoutSessionForm — CreateWorkoutSessionForm - validates session metadata, builds exercise rows, calls createWorkoutSession, and redirects to the member detail page on success.</t>
   </si>
@@ -63,18 +63,6 @@
     <t>createWorkoutSession(valid session, parsed rows) is called once on valid submit; router.push(`/admin/members/${memberId}`) is called on success.</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Run: npx jest create-workout-session-form.test.tsx --selectProjects jsdom</t>
-  </si>
-  <si>
-    <t>Suite is kept in a single main describe block and covers metadata validation predicates, row mutation branches, server action outcomes, and pending UI state.</t>
-  </si>
-  <si>
-    <t>The form uses noValidate so client schema validation, rather than browser constraint validation, is exercised in JSDOM.</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -183,12 +171,24 @@
     <t>Select member, set valid date, and set Notes to 1025 characters.</t>
   </si>
   <si>
-    <t>Validation failed alert visible; createWorkoutSession not called.</t>
+    <t>Validation failed alert and Notes max-length field error visible; createWorkoutSession not called.</t>
   </si>
   <si>
     <t>TC-08</t>
   </si>
   <si>
+    <t>Rejects an invalid exercise row and does not call create.</t>
+  </si>
+  <si>
+    <t>Select member, set valid date, leave Exercise empty, and set sets/reps/weight above their upper bounds.</t>
+  </si>
+  <si>
+    <t>Validation failed plus Exercise, Sets, Reps, and Weight field errors are visible; createWorkoutSession not called.</t>
+  </si>
+  <si>
+    <t>TC-09</t>
+  </si>
+  <si>
     <t>Adds a second exercise row and enables removal.</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t>Member select plus two exercise selects exist; two Remove buttons exist and the first is enabled.</t>
   </si>
   <si>
-    <t>TC-09</t>
+    <t>TC-10</t>
   </si>
   <si>
     <t>Removes the second exercise row and disables the remaining Remove button.</t>
@@ -216,7 +216,7 @@
     <t>Member select plus one exercise select remain; the sole Remove button is disabled.</t>
   </si>
   <si>
-    <t>TC-10</t>
+    <t>TC-11</t>
   </si>
   <si>
     <t>Submits edited metadata and row values, then navigates to member detail.</t>
@@ -228,7 +228,7 @@
     <t>createWorkoutSession called with trimmed notes and numeric row values; router.push /admin/members/mem-1.</t>
   </si>
   <si>
-    <t>TC-11</t>
+    <t>TC-12</t>
   </si>
   <si>
     <t>Submits an added exercise row as a second parsed row.</t>
@@ -240,7 +240,7 @@
     <t>createWorkoutSession receives two parsed exercise rows; router.push /admin/members/mem-1.</t>
   </si>
   <si>
-    <t>TC-12</t>
+    <t>TC-13</t>
   </si>
   <si>
     <t>Shows server error and does not navigate when create fails.</t>
@@ -252,7 +252,7 @@
     <t>Server error visible; Create Session enabled; create called once; router.push not called.</t>
   </si>
   <si>
-    <t>TC-13</t>
+    <t>TC-14</t>
   </si>
   <si>
     <t>Displays returned server field errors for editable metadata.</t>
@@ -264,7 +264,7 @@
     <t>Validation failed alert and returned member/date/duration errors are visible; router.push not called.</t>
   </si>
   <si>
-    <t>TC-14</t>
+    <t>TC-15</t>
   </si>
   <si>
     <t>Disables submit control while create is pending.</t>
@@ -765,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -854,50 +854,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -906,7 +867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -922,22 +883,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -945,22 +906,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="G2" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -968,22 +929,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -991,22 +952,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1014,22 +975,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1037,22 +998,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1060,45 +1021,45 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="G8" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1106,22 +1067,22 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1129,22 +1090,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1152,22 +1113,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1175,22 +1136,22 @@
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1198,22 +1159,22 @@
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1221,22 +1182,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,22 +1205,45 @@
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>31</v>
+      <c r="G16" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1355,10 +1339,10 @@
         <v>98</v>
       </c>
       <c r="C6" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
